--- a/Production/QuoteSheet.xlsx
+++ b/Production/QuoteSheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Augenblick/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Augenblick/Documents/2025Summer/FreeCAD/Boards/PyOpticL_Rubidium_System/Production/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D62E73-4FEC-DC43-B468-2E33722459B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0631BD3E-5319-6246-8288-FFFB036B9065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-36440" yWindow="-5520" windowWidth="29860" windowHeight="18960" xr2:uid="{70307406-910B-D446-B246-AFD9F07E1F57}"/>
   </bookViews>
@@ -82,9 +82,6 @@
     <t>SAS-Baseplate.step</t>
   </si>
   <si>
-    <t>Split_Baseplate.step</t>
-  </si>
-  <si>
     <t>Iris_Adapter.step</t>
   </si>
   <si>
@@ -95,6 +92,9 @@
   </si>
   <si>
     <t>reference_baseplate.step</t>
+  </si>
+  <si>
+    <t>Repumper_Baseplate.step</t>
   </si>
 </sst>
 </file>
@@ -526,7 +526,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -574,7 +574,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>4</v>
@@ -582,7 +582,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B20">
         <v>3</v>
